--- a/artfynd/A 6285-2024 artfynd.xlsx
+++ b/artfynd/A 6285-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118368629</v>
+        <v>118368052</v>
       </c>
       <c r="B2" t="n">
         <v>97846</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497897</v>
+        <v>497926</v>
       </c>
       <c r="R2" t="n">
-        <v>6912168</v>
+        <v>6912222</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Knärot på hygge som höggs 4 månader sen</t>
+          <t>Knärot på hygge som avverkades 4 månader sen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118368052</v>
+        <v>118368629</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497926</v>
+        <v>497897</v>
       </c>
       <c r="R3" t="n">
-        <v>6912222</v>
+        <v>6912168</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Knärot på hygge som avverkades 4 månader sen</t>
+          <t>Knärot på hygge som höggs 4 månader sen</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 6285-2024 artfynd.xlsx
+++ b/artfynd/A 6285-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118368052</v>
+        <v>118368629</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497926</v>
+        <v>497897</v>
       </c>
       <c r="R2" t="n">
-        <v>6912222</v>
+        <v>6912168</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Knärot på hygge som avverkades 4 månader sen</t>
+          <t>Knärot på hygge som höggs 4 månader sen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118368629</v>
+        <v>118368052</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497897</v>
+        <v>497926</v>
       </c>
       <c r="R3" t="n">
-        <v>6912168</v>
+        <v>6912222</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Knärot på hygge som höggs 4 månader sen</t>
+          <t>Knärot på hygge som avverkades 4 månader sen</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 6285-2024 artfynd.xlsx
+++ b/artfynd/A 6285-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118368629</v>
+        <v>118368052</v>
       </c>
       <c r="B2" t="n">
         <v>97853</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497897</v>
+        <v>497926</v>
       </c>
       <c r="R2" t="n">
-        <v>6912168</v>
+        <v>6912222</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Knärot på hygge som höggs 4 månader sen</t>
+          <t>Knärot på hygge som avverkades 4 månader sen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118368052</v>
+        <v>118368629</v>
       </c>
       <c r="B3" t="n">
         <v>97853</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497926</v>
+        <v>497897</v>
       </c>
       <c r="R3" t="n">
-        <v>6912222</v>
+        <v>6912168</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Knärot på hygge som avverkades 4 månader sen</t>
+          <t>Knärot på hygge som höggs 4 månader sen</t>
         </is>
       </c>
       <c r="AD3" t="b">
